--- a/artfynd/S 558-2024 artfynd.xlsx
+++ b/artfynd/S 558-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/684141</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1886986</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14191229</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14191267</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13753870</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14196787</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14191327</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1611,6 +1651,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14191320</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1732,6 +1777,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14191321</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1848,6 +1898,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14191255</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1964,6 +2019,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14191256</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2080,6 +2140,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14191257</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2190,6 +2255,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83308057</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2300,6 +2370,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83308058</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2410,6 +2485,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83308061</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2520,6 +2600,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83308062</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2630,6 +2715,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83308063</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2740,6 +2830,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83308065</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2850,6 +2945,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83308453</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2960,6 +3060,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83308461</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3070,6 +3175,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83308705</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3180,6 +3290,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310244</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3290,6 +3405,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310247</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3400,6 +3520,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310264</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3510,6 +3635,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310296</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3620,6 +3750,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310312</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3730,6 +3865,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310316</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3840,6 +3980,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310330</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3950,6 +4095,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310333</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4060,6 +4210,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310335</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4170,6 +4325,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310360</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4280,6 +4440,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310362</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4390,6 +4555,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310376</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4500,6 +4670,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310378</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4610,8 +4785,50 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83310393</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>